--- a/AAII_Financials/Yearly/VST_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VST_YR_FIN.xlsx
@@ -2974,10 +2974,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4254000</v>
+        <v>4886000</v>
       </c>
       <c r="E58" s="3">
-        <v>1670000</v>
+        <v>2373000</v>
       </c>
       <c r="F58" s="3">
         <v>2326000</v>
@@ -3025,10 +3025,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5496000</v>
+        <v>4864000</v>
       </c>
       <c r="E59" s="3">
-        <v>4842000</v>
+        <v>4139000</v>
       </c>
       <c r="F59" s="3">
         <v>5932000</v>
@@ -3130,7 +3130,7 @@
         <v>16163000</v>
       </c>
       <c r="E61" s="3">
-        <v>15743000</v>
+        <v>16375000</v>
       </c>
       <c r="F61" s="3">
         <v>12415000</v>
@@ -3181,7 +3181,7 @@
         <v>7312000</v>
       </c>
       <c r="E62" s="3">
-        <v>7190000</v>
+        <v>6558000</v>
       </c>
       <c r="F62" s="3">
         <v>5158000</v>
